--- a/doc/airsens-duree-vie-bat.xlsx
+++ b/doc/airsens-duree-vie-bat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f34ccaa6039d8a87/technique/_projets/esp32-micropython/esp32-airsens/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="192" documentId="11_AD4D9D64A577C15A4A541867889B64EE5BDEDD89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B9B2139-7B96-40E8-A428-D8A2BF5CA603}"/>
+  <xr:revisionPtr revIDLastSave="212" documentId="11_AD4D9D64A577C15A4A541867889B64EE5BDEDD89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D407C98-D0F7-4ADD-BBD9-DEB649CAC0A5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>Batterie</t>
   </si>
@@ -107,6 +107,12 @@
   </si>
   <si>
     <t>PPK</t>
+  </si>
+  <si>
+    <t>essai longue durée</t>
+  </si>
+  <si>
+    <t>05,06,2022</t>
   </si>
 </sst>
 </file>
@@ -182,7 +188,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -281,7 +287,57 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
@@ -294,53 +350,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
+      <left/>
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -359,122 +378,124 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -760,7 +781,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -780,219 +801,288 @@
     <col min="16" max="16" width="7.28515625" style="3" customWidth="1"/>
     <col min="17" max="17" width="8.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.140625" style="3"/>
+    <col min="20" max="20" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="14" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="15"/>
-      <c r="H1" s="12" t="s">
+      <c r="G1" s="39"/>
+      <c r="H1" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="13"/>
-      <c r="J1" s="7" t="s">
+      <c r="I1" s="44"/>
+      <c r="J1" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="17" t="s">
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="18"/>
-      <c r="P1" s="5" t="s">
+      <c r="O1" s="34"/>
+      <c r="P1" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="6"/>
+      <c r="Q1" s="32"/>
       <c r="R1" s="3"/>
     </row>
-    <row r="2" spans="1:19" ht="113.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:21" ht="113.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="J2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="29" t="s">
+      <c r="N2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="30" t="s">
+      <c r="O2" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="31" t="s">
+      <c r="P2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="32" t="s">
+      <c r="Q2" s="18" t="s">
         <v>20</v>
       </c>
       <c r="R2" s="4"/>
       <c r="S2" s="2"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="20">
         <v>2.8</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="20">
         <v>2</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="20">
         <v>1.5</v>
       </c>
-      <c r="E3" s="35">
+      <c r="E3" s="21">
         <v>1</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3" s="19">
         <v>20</v>
       </c>
-      <c r="G3" s="35">
+      <c r="G3" s="21">
         <v>5</v>
       </c>
-      <c r="H3" s="33">
+      <c r="H3" s="19">
         <v>0.34</v>
       </c>
-      <c r="I3" s="36">
+      <c r="I3" s="22">
         <v>1E-4</v>
       </c>
-      <c r="J3" s="37">
+      <c r="J3" s="23">
         <f>3600/F3</f>
         <v>180</v>
       </c>
-      <c r="K3" s="38">
+      <c r="K3" s="24">
         <f>H3/3600</f>
         <v>9.4444444444444456E-5</v>
       </c>
-      <c r="L3" s="39">
+      <c r="L3" s="25">
         <f>J3*G3</f>
         <v>900</v>
       </c>
-      <c r="M3" s="44">
+      <c r="M3" s="30">
         <f>K3*J3</f>
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="N3" s="40">
+      <c r="N3" s="26">
         <f>3600-L3</f>
         <v>2700</v>
       </c>
-      <c r="O3" s="43">
+      <c r="O3" s="29">
         <f>I3*N3/3600</f>
         <v>7.5000000000000007E-5</v>
       </c>
-      <c r="P3" s="41">
+      <c r="P3" s="27">
         <f>M3+O3</f>
         <v>1.7075E-2</v>
       </c>
-      <c r="Q3" s="42">
+      <c r="Q3" s="28">
         <f>B3/P3</f>
         <v>163.98243045387994</v>
       </c>
-      <c r="R3" s="3">
-        <f>Q3/24</f>
-        <v>6.832601268911664</v>
-      </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="20">
         <v>2.8</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="20">
         <v>2</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="20">
         <v>1.5</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="21">
         <v>1</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="19">
         <v>900</v>
       </c>
-      <c r="G4" s="35">
+      <c r="G4" s="21">
         <v>5</v>
       </c>
-      <c r="H4" s="33">
+      <c r="H4" s="19">
         <v>0.23</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="22">
         <v>6.0000000000000002E-5</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="23">
         <f>3600/F4</f>
         <v>4</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="24">
         <f>H4/3600</f>
         <v>6.3888888888888895E-5</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="25">
         <f>J4*G4</f>
         <v>20</v>
       </c>
-      <c r="M4" s="44">
+      <c r="M4" s="30">
         <f>K4*J4</f>
         <v>2.5555555555555558E-4</v>
       </c>
-      <c r="N4" s="40">
+      <c r="N4" s="26">
         <f>3600-L4</f>
         <v>3580</v>
       </c>
-      <c r="O4" s="43">
+      <c r="O4" s="29">
         <f>I4*N4/3600</f>
         <v>5.9666666666666669E-5</v>
       </c>
-      <c r="P4" s="41">
+      <c r="P4" s="27">
         <f>M4+O4</f>
         <v>3.1522222222222227E-4</v>
       </c>
-      <c r="Q4" s="42">
+      <c r="Q4" s="28">
         <f>B4/P4</f>
         <v>8882.6224885442352</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="20">
+        <v>2</v>
+      </c>
+      <c r="C6" s="20">
+        <v>2</v>
+      </c>
+      <c r="D6" s="20">
+        <v>1.5</v>
+      </c>
+      <c r="E6" s="21">
+        <v>1</v>
+      </c>
+      <c r="F6" s="19">
+        <v>19</v>
+      </c>
+      <c r="G6" s="21">
+        <v>4</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0.18</v>
+      </c>
+      <c r="I6" s="22">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="J6" s="23">
+        <f>3600/F6</f>
+        <v>189.47368421052633</v>
+      </c>
+      <c r="K6" s="24">
+        <f>H6/3600</f>
+        <v>4.9999999999999996E-5</v>
+      </c>
+      <c r="L6" s="25">
+        <f>J6*G6</f>
+        <v>757.89473684210532</v>
+      </c>
+      <c r="M6" s="30">
+        <f>K6*J6</f>
+        <v>9.4736842105263164E-3</v>
+      </c>
+      <c r="N6" s="26">
+        <f>3600-L6</f>
+        <v>2842.1052631578946</v>
+      </c>
+      <c r="O6" s="29">
+        <f>I6*N6/3600</f>
+        <v>4.7368421052631574E-5</v>
+      </c>
+      <c r="P6" s="27">
+        <f>M6+O6</f>
+        <v>9.5210526315789475E-3</v>
+      </c>
+      <c r="Q6" s="28">
+        <f>B6/P6</f>
+        <v>210.06080707573244</v>
+      </c>
+      <c r="R6" s="3">
+        <f>Q6/24</f>
+        <v>8.7525336281555184</v>
+      </c>
+      <c r="T6" t="s">
+        <v>24</v>
+      </c>
+      <c r="U6" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/doc/airsens-duree-vie-bat.xlsx
+++ b/doc/airsens-duree-vie-bat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f34ccaa6039d8a87/technique/_projets/esp32-micropython/esp32-airsens/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="11_AD4D9D64A577C15A4A541867889B64EE5BDEDD89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D407C98-D0F7-4ADD-BBD9-DEB649CAC0A5}"/>
+  <xr:revisionPtr revIDLastSave="220" documentId="11_AD4D9D64A577C15A4A541867889B64EE5BDEDD89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0538ACED-BC4C-4F3A-9921-10A264DE736F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,9 +52,6 @@
     <t>Nbre</t>
   </si>
   <si>
-    <t xml:space="preserve">U nom  èv </t>
-  </si>
-  <si>
     <t>U min"[V]</t>
   </si>
   <si>
@@ -113,6 +110,9 @@
   </si>
   <si>
     <t>05,06,2022</t>
+  </si>
+  <si>
+    <t>U nom  [V]</t>
   </si>
 </sst>
 </file>
@@ -788,7 +788,7 @@
     <col min="2" max="2" width="4" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="4" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="4.5703125" style="3" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -814,25 +814,25 @@
       <c r="D1" s="36"/>
       <c r="E1" s="37"/>
       <c r="F1" s="38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1" s="39"/>
       <c r="H1" s="43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I1" s="44"/>
       <c r="J1" s="40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K1" s="41"/>
       <c r="L1" s="41"/>
       <c r="M1" s="42"/>
       <c r="N1" s="33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O1" s="34"/>
       <c r="P1" s="31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q1" s="32"/>
       <c r="R1" s="3"/>
@@ -842,52 +842,52 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>5</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>6</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="I2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="11" t="s">
-        <v>9</v>
-      </c>
       <c r="J2" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K2" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="M2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="N2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="O2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="P2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="Q2" s="18" t="s">
         <v>19</v>
-      </c>
-      <c r="Q2" s="18" t="s">
-        <v>20</v>
       </c>
       <c r="R2" s="4"/>
       <c r="S2" s="2"/>
@@ -1019,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="20">
         <v>2</v>
@@ -1028,7 +1028,7 @@
         <v>1.5</v>
       </c>
       <c r="E6" s="21">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="F6" s="19">
         <v>19</v>
@@ -1072,17 +1072,17 @@
       </c>
       <c r="Q6" s="28">
         <f>B6/P6</f>
-        <v>210.06080707573244</v>
+        <v>105.03040353786622</v>
       </c>
       <c r="R6" s="3">
         <f>Q6/24</f>
-        <v>8.7525336281555184</v>
+        <v>4.3762668140777592</v>
       </c>
       <c r="T6" t="s">
+        <v>23</v>
+      </c>
+      <c r="U6" t="s">
         <v>24</v>
-      </c>
-      <c r="U6" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/doc/airsens-duree-vie-bat.xlsx
+++ b/doc/airsens-duree-vie-bat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f34ccaa6039d8a87/technique/_projets/esp32-micropython/esp32-airsens/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="220" documentId="11_AD4D9D64A577C15A4A541867889B64EE5BDEDD89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0538ACED-BC4C-4F3A-9921-10A264DE736F}"/>
+  <xr:revisionPtr revIDLastSave="244" documentId="11_AD4D9D64A577C15A4A541867889B64EE5BDEDD89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50227CC1-445B-4FA1-B242-1365554A5A96}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>Batterie</t>
   </si>
@@ -107,9 +107,6 @@
   </si>
   <si>
     <t>essai longue durée</t>
-  </si>
-  <si>
-    <t>05,06,2022</t>
   </si>
   <si>
     <t>U nom  [V]</t>
@@ -366,7 +363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -456,6 +453,7 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -806,35 +804,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="39"/>
-      <c r="H1" s="43" t="s">
+      <c r="G1" s="40"/>
+      <c r="H1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="44"/>
-      <c r="J1" s="40" t="s">
+      <c r="I1" s="45"/>
+      <c r="J1" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="33" t="s">
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="34"/>
-      <c r="P1" s="31" t="s">
+      <c r="O1" s="35"/>
+      <c r="P1" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="32"/>
+      <c r="Q1" s="33"/>
       <c r="R1" s="3"/>
     </row>
     <row r="2" spans="1:21" ht="113.25" x14ac:dyDescent="0.25">
@@ -848,7 +846,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>5</v>
@@ -897,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="20">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="C3" s="20">
         <v>2</v>
@@ -915,10 +913,10 @@
         <v>5</v>
       </c>
       <c r="H3" s="19">
-        <v>0.34</v>
+        <v>0.18</v>
       </c>
       <c r="I3" s="22">
-        <v>1E-4</v>
+        <v>6.0000000000000002E-5</v>
       </c>
       <c r="J3" s="23">
         <f>3600/F3</f>
@@ -926,7 +924,7 @@
       </c>
       <c r="K3" s="24">
         <f>H3/3600</f>
-        <v>9.4444444444444456E-5</v>
+        <v>4.9999999999999996E-5</v>
       </c>
       <c r="L3" s="25">
         <f>J3*G3</f>
@@ -934,7 +932,7 @@
       </c>
       <c r="M3" s="30">
         <f>K3*J3</f>
-        <v>1.7000000000000001E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="N3" s="26">
         <f>3600-L3</f>
@@ -942,15 +940,19 @@
       </c>
       <c r="O3" s="29">
         <f>I3*N3/3600</f>
-        <v>7.5000000000000007E-5</v>
+        <v>4.5000000000000003E-5</v>
       </c>
       <c r="P3" s="27">
         <f>M3+O3</f>
-        <v>1.7075E-2</v>
+        <v>9.0449999999999992E-3</v>
       </c>
       <c r="Q3" s="28">
         <f>B3/P3</f>
-        <v>163.98243045387994</v>
+        <v>276.39579878385848</v>
+      </c>
+      <c r="R3" s="3">
+        <f>Q3/24</f>
+        <v>11.516491615994104</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -958,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="20">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="C4" s="20">
         <v>2</v>
@@ -1011,7 +1013,11 @@
       </c>
       <c r="Q4" s="28">
         <f>B4/P4</f>
-        <v>8882.6224885442352</v>
+        <v>7930.9129362002104</v>
+      </c>
+      <c r="R4" s="3">
+        <f>Q4/24</f>
+        <v>330.45470567500877</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -1031,10 +1037,10 @@
         <v>1.3</v>
       </c>
       <c r="F6" s="19">
-        <v>19</v>
+        <v>300</v>
       </c>
       <c r="G6" s="21">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="H6" s="19">
         <v>0.18</v>
@@ -1044,7 +1050,7 @@
       </c>
       <c r="J6" s="23">
         <f>3600/F6</f>
-        <v>189.47368421052633</v>
+        <v>12</v>
       </c>
       <c r="K6" s="24">
         <f>H6/3600</f>
@@ -1052,37 +1058,37 @@
       </c>
       <c r="L6" s="25">
         <f>J6*G6</f>
-        <v>757.89473684210532</v>
+        <v>45.599999999999994</v>
       </c>
       <c r="M6" s="30">
         <f>K6*J6</f>
-        <v>9.4736842105263164E-3</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="N6" s="26">
         <f>3600-L6</f>
-        <v>2842.1052631578946</v>
+        <v>3554.4</v>
       </c>
       <c r="O6" s="29">
         <f>I6*N6/3600</f>
-        <v>4.7368421052631574E-5</v>
+        <v>5.9240000000000002E-5</v>
       </c>
       <c r="P6" s="27">
         <f>M6+O6</f>
-        <v>9.5210526315789475E-3</v>
+        <v>6.5923999999999996E-4</v>
       </c>
       <c r="Q6" s="28">
         <f>B6/P6</f>
-        <v>105.03040353786622</v>
+        <v>1516.8982464656272</v>
       </c>
       <c r="R6" s="3">
         <f>Q6/24</f>
-        <v>4.3762668140777592</v>
+        <v>63.204093602734467</v>
       </c>
       <c r="T6" t="s">
         <v>23</v>
       </c>
-      <c r="U6" t="s">
-        <v>24</v>
+      <c r="U6" s="31">
+        <v>44721</v>
       </c>
     </row>
   </sheetData>
